--- a/docs/ValueSet-ahip-background-white-category.xlsx
+++ b/docs/ValueSet-ahip-background-white-category.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
   <si>
     <t>Property</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,6 +87,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Used as the granular follow-up answer options shown when the patient selects White or European on the race/ethnicity question.</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -153,12 +156,6 @@
     <t>urn:oid:2.16.840.1.113883.6.238</t>
   </si>
   <si>
-    <t>9999-19</t>
-  </si>
-  <si>
-    <t>Saudi</t>
-  </si>
-  <si>
     <t>9999-20</t>
   </si>
   <si>
@@ -231,7 +228,7 @@
     <t>Welsh</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-background-codes</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-background-codes</t>
   </si>
   <si>
     <t>ASKU</t>
@@ -255,7 +252,7 @@
     <t>Please specify if not listed above</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -489,29 +486,29 @@
         <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -530,7 +527,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -538,58 +535,58 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -602,10 +599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -615,7 +612,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -624,7 +621,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -632,122 +629,114 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>70</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -766,7 +755,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -774,10 +763,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -790,10 +779,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +801,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -820,18 +809,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -844,10 +833,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-background-white-category.xlsx
+++ b/docs/ValueSet-ahip-background-white-category.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="77">
   <si>
     <t>Property</t>
   </si>
@@ -244,12 +244,6 @@
   </si>
   <si>
     <t>I choose not to respond at this time</t>
-  </si>
-  <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
@@ -792,7 +786,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -817,26 +811,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-background-white-category.xlsx
+++ b/docs/ValueSet-ahip-background-white-category.xlsx
@@ -96,7 +96,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>Most of the information on the CDC and ATSDR websites is not subject to copyright, is in the public domain, and may be freely used or reproduced without obtaining copyright permission. For information and exceptions regarding use of CDC material please see https://www.cdc.gov/other/agencymaterials.html.
+This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -228,7 +230,7 @@
     <t>Welsh</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-background-codes</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-temporary-codes</t>
   </si>
   <si>
     <t>ASKU</t>
@@ -246,7 +248,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
